--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2412-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2412-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7659E158-1C4C-470A-B62E-1BFDB524BE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3EA9313-7728-4E23-9F5F-8EBA606C7524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{93F5D9D6-39EF-40E9-ACA6-490709A67E58}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{A2E9D29B-67B5-4BBF-B73E-55BDEF9E1F71}"/>
   </bookViews>
   <sheets>
     <sheet name="2412-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1487,27 +1487,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9774DD2-E851-4880-AC46-3EB737522DE2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3BE6E5B-74FB-4D7A-913E-B899B41AF4A6}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1541,7 +1540,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1577,7 +1576,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1629,7 +1628,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1697,7 +1696,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1769,7 +1768,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1841,7 +1840,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1913,7 +1912,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -1985,7 +1984,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2057,7 +2056,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2129,7 +2128,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2018</v>
       </c>
@@ -2201,7 +2200,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2017</v>
       </c>
@@ -2273,7 +2272,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2016</v>
       </c>
@@ -2345,7 +2344,7 @@
         <v>4.97</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2015</v>
       </c>
@@ -2417,7 +2416,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2014</v>
       </c>
@@ -2489,7 +2488,7 @@
         <v>5.27</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2013</v>
       </c>
@@ -2561,7 +2560,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2012</v>
       </c>
@@ -2633,7 +2632,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2011</v>
       </c>
@@ -2705,7 +2704,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2010</v>
       </c>
@@ -2777,7 +2776,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2009</v>
       </c>
@@ -2849,7 +2848,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2008</v>
       </c>
@@ -2921,7 +2920,7 @@
         <v>9.66</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2007</v>
       </c>
@@ -2993,7 +2992,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2006</v>
       </c>
@@ -3065,7 +3064,7 @@
         <v>9.0299999999999994</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2005</v>
       </c>
@@ -3137,7 +3136,7 @@
         <v>8.41</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2004</v>
       </c>
@@ -3209,7 +3208,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2003</v>
       </c>
@@ -3281,7 +3280,7 @@
         <v>9.11</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2002</v>
       </c>
@@ -3353,7 +3352,7 @@
         <v>8.73</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2001</v>
       </c>
@@ -3425,7 +3424,7 @@
         <v>8.18</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2000</v>
       </c>
@@ -3497,7 +3496,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>1999</v>
       </c>
@@ -3569,7 +3568,7 @@
         <v>6.43</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>1998</v>
       </c>
@@ -3641,7 +3640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1997</v>
       </c>
@@ -3713,7 +3712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35" t="s">
         <v>53</v>
       </c>
